--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -24,8 +24,11 @@
     <sheet name="SERIES" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="CLUBS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="META" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$12</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +51,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,12 +96,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -16374,7 +16392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16418,6 +16436,148 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1996_97_0266 'Art. Pardubice' prev→CLUB_S1995_96_0285 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1996_97_0294 'Choceň B' prev→CLUB_S1995_96_0274 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1996_97_0401 'Z club Zlín' prev→CLUB_S1995_96_0399 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1996_97_0441 'SK Poruba' prev→CLUB_S1995_96_0414 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1996_97_0468 'HC Donau České Budějovice' prev→CLUB_S1995_96_0160 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1996_97_0081 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1996_97_0086 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1996_97_0087 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1996_97_0088 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0021</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1996_97_0021 'Baráž o Extraligu' (L15, parent=NODE_S1996_97_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0027</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1996_97_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1996_97_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -19909,8 +20069,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -19990,7 +20148,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -42588,6 +42745,303 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0266</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0266 'Art. Pardubice' prev→CLUB_S1995_96_0285 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0294</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0294 'Choceň B' prev→CLUB_S1995_96_0274 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0401</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0401 'Z club Zlín' prev→CLUB_S1995_96_0399 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0441</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0441 'SK Poruba' prev→CLUB_S1995_96_0414 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0468</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0468 'HC Donau České Budějovice' prev→CLUB_S1995_96_0160 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0081</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0081 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0086</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0086 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0087</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0087 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0088</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0088 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0021</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1996_97_0021 'Baráž o Extraligu' (L15, parent=NODE_S1996_97_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0027</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1996_97_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1996_97_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16392,7 +16392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16442,7 +16442,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1996_97_0266 'Art. Pardubice' prev→CLUB_S1995_96_0285 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1996_97_0294 'Choceň B' prev→CLUB_S1995_96_0274 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16466,7 +16466,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1996_97_0401 'Z club Zlín' prev→CLUB_S1995_96_0399 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16478,7 +16478,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1996_97_0441 'SK Poruba' prev→CLUB_S1995_96_0414 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -16490,7 +16490,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1996_97_0468 'HC Donau České Budějovice' prev→CLUB_S1995_96_0160 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -16502,7 +16502,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1996_97_0081 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -16514,7 +16514,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1996_97_0086 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -16526,7 +16526,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1996_97_0087 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1996_97_0088 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16548,14 +16548,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NODE_S1996_97_0021</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1996_97_0021 'Baráž o Extraligu' (L15, parent=NODE_S1996_97_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16565,17 +16560,384 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NODE_S1996_97_0027</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1996_97_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1996_97_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20069,6 +20431,8 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -20099,6 +20463,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0001</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -20111,6 +20480,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0003</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -20123,6 +20497,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0003</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -20135,6 +20514,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0032</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -20148,6 +20532,7 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -22340,12 +22725,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -22466,12 +22851,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22765,12 +23150,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -23106,12 +23491,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -23274,12 +23659,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -23820,12 +24205,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -23862,12 +24247,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -24707,12 +25092,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -24885,12 +25270,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -24932,12 +25317,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28740,12 +29125,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28908,12 +29293,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -29301,12 +29686,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -29343,12 +29728,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29761,12 +30146,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -30038,12 +30423,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30085,12 +30470,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -30179,12 +30564,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31371,12 +31756,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Tábor = Klub rozhodčích LH Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Klub rozhodci ledniho hokeje. city Tábor.</t>
+          <t>Tábor = Klub rozhodčích LH Tábor (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj. Klub rozhodci ledniho hokeje. city Tábor. || TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Klub rozhodčích LH Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -33042,12 +33427,12 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -33252,12 +33637,12 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -33467,12 +33852,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -39456,12 +39841,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Zlín = TJ Z-club Zlín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. Patterns: Z-klub Zlín. city Zlín. || TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>Zlín = TJ Z-club Zlín (Wiki D42 - registr ustavy 04/2026). Zlinsky kraj. Patterns: Z-klub Zlín. city Zlín. || TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity] || TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Z club Zlín</t>
+          <t>Zlín</t>
         </is>
       </c>
     </row>
@@ -39785,12 +40170,12 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -39832,12 +40217,12 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -40927,12 +41312,12 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava.</t>
+          <t>Ostrava = TJ NH Válcovny Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **NH** = Nová huť. **Válcovny** = oddeleni NH. city Ostrava. || TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>NH Válcovny Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -41471,12 +41856,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -42755,11 +43140,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -42804,21 +43189,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0266</t>
+          <t>CLUB_S1996_97_0004</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0266 'Art. Pardubice' prev→CLUB_S1995_96_0285 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -42826,21 +43209,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0294</t>
+          <t>CLUB_S1996_97_0007</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0294 'Choceň B' prev→CLUB_S1995_96_0274 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -42848,21 +43229,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0401</t>
+          <t>CLUB_S1996_97_0014</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0401 'Z club Zlín' prev→CLUB_S1995_96_0399 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -42870,21 +43249,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0441</t>
+          <t>CLUB_S1996_97_0022</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0441 'SK Poruba' prev→CLUB_S1995_96_0414 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -42892,21 +43269,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0468</t>
+          <t>CLUB_S1996_97_0026</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0468 'HC Donau České Budějovice' prev→CLUB_S1995_96_0160 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -42914,21 +43289,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0081</t>
+          <t>CLUB_S1996_97_0041</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0081 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -42936,21 +43309,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0086</t>
+          <t>CLUB_S1996_97_0042</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0086 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -42958,21 +43329,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0087</t>
+          <t>CLUB_S1996_97_0062</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0087 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -42980,21 +43349,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0088</t>
+          <t>CLUB_S1996_97_0066</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0088 fate nekonzist. ['sestup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -43002,21 +43369,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NODE_S1996_97_0021</t>
+          <t>CLUB_S1996_97_0067</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1996_97_0021 'Baráž o Extraligu' (L15, parent=NODE_S1996_97_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -43024,24 +43389,642 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S1996_97_0027</t>
+          <t>CLUB_S1996_97_0083</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1996_97_0027 'Baráž o 1.ligu' (L20, parent=NODE_S1996_97_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0107</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0152</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0156</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0156</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0165</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0165</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0166</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0175</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0181</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0182</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0184</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0192</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0210</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0250</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0251</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0256</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0260</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0262</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0266</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0288</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0294</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0304</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0401</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0401</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0408</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0409</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0435</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0441</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0447</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0468</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1996_97_0471</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11869,7 +11869,11 @@
           <t>CLUB_S1996_97_0384</t>
         </is>
       </c>
-      <c r="R74" s="3" t="n"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0380</t>
+        </is>
+      </c>
       <c r="S74" s="3" t="n"/>
       <c r="T74" s="3" t="n"/>
       <c r="U74" s="3" t="n"/>
@@ -16392,7 +16396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16454,7 +16458,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16466,7 +16470,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16478,7 +16482,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -16490,7 +16494,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -16502,7 +16506,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -16514,7 +16518,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -16526,7 +16530,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16538,7 +16542,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16550,7 +16554,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16562,7 +16566,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16574,7 +16578,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16586,7 +16590,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16598,7 +16602,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -16610,7 +16614,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -16622,7 +16626,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -16634,7 +16638,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16646,7 +16650,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16658,7 +16662,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16670,7 +16674,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -16682,7 +16686,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16694,7 +16698,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16706,7 +16710,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -16718,7 +16722,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -16730,7 +16734,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16742,7 +16746,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16754,7 +16758,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -16766,7 +16770,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16778,7 +16782,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16790,7 +16794,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16802,7 +16806,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16814,7 +16818,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16826,7 +16830,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16838,106 +16842,10 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16954,7 +16862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17013,6 +16921,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17055,6 +16968,11 @@
           <t>14 týmů: základ + QF/SF/finále/O3 + baráž. Mistr: HC Petra Vsetín.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17102,6 +17020,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17144,6 +17067,11 @@
           <t>1.liga: základní část + play-off + baráž o 1.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17186,6 +17114,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17228,6 +17161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17270,6 +17208,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17312,6 +17255,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17354,6 +17302,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17396,6 +17349,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17438,6 +17396,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17480,6 +17443,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17522,6 +17490,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17564,6 +17537,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17606,6 +17584,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17648,6 +17631,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17690,6 +17678,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17732,6 +17725,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17774,6 +17772,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17816,6 +17819,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17858,6 +17866,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -17900,6 +17913,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17942,6 +17960,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17984,6 +18007,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18026,6 +18054,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18068,6 +18101,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18110,6 +18148,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18157,6 +18200,11 @@
           <t>Baráž o 1.ligu: Karviná – Třebíč 0:4, Sokolov – Znojmo 0:4.</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -18204,6 +18252,11 @@
           <t>Kvalifikace o 2.ligu</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18246,6 +18299,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18372,6 +18430,11 @@
           <t>II.liga: 2 skupiny + 1.kolo + 2.kolo.</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0035</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18414,6 +18477,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0036</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -18456,6 +18524,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0037</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18624,6 +18697,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0041</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18750,6 +18828,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0048</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18792,6 +18875,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0050</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -19086,6 +19174,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0051</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -19128,6 +19221,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0052</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -19170,6 +19268,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0053</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -19212,6 +19315,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0054</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -19254,6 +19362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0055</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -19296,6 +19409,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0056</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -19338,6 +19456,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0057</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19380,6 +19503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0058</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19422,6 +19550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0059</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19464,6 +19597,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0060</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -19506,6 +19644,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0062</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19548,6 +19691,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0063</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -19590,6 +19738,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0064</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -19632,6 +19785,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0065</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19674,6 +19832,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0066</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19716,6 +19879,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0067</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -19758,6 +19926,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0068</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -19800,6 +19973,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0069</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -19842,6 +20020,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0070</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -19884,6 +20067,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0071</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -19926,6 +20114,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0072</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -19968,6 +20161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0070</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20010,6 +20208,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0071</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20388,6 +20591,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0084</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -20428,6 +20636,11 @@
       <c r="K82" t="inlineStr">
         <is>
           <t>Kontejner L50</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1995_96_0085</t>
         </is>
       </c>
     </row>
@@ -20451,6 +20664,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -20468,6 +20686,11 @@
           <t>NODE_S1996_97_0001</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -20485,6 +20708,11 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -20502,6 +20730,11 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -20519,6 +20752,11 @@
           <t>NODE_S1996_97_0032</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -20529,6 +20767,11 @@
       <c r="B91" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -22851,12 +23094,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23150,12 +23393,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -24247,12 +24490,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -25317,12 +25560,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -29125,12 +29368,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29293,12 +29536,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -29686,12 +29929,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -29728,12 +29971,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39055,9 +39298,14 @@
           <t>Kroměříž + Přerov</t>
         </is>
       </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>CLUB_S1995_96_0380</t>
+        </is>
+      </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>Chomýž u Kroměříže = TJ Sokol Chomýž (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž, district 'Kroměříž' potvrzen). POZOR: vícero - Chomýž u Krnova (Severomoravsky/Bruntál), Chomýž u Bruntálu. city Chomýž u Kroměříže.</t>
+          <t>Chomýž u Kroměříže = TJ Sokol Chomýž (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kroměříž, district 'Kroměříž' potvrzen). POZOR: vícero - Chomýž u Krnova (Severomoravsky/Bruntál), Chomýž u Bruntálu. city Chomýž u Kroměříže. || TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -41856,12 +42104,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -43140,7 +43388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -43214,12 +43462,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0007</t>
+          <t>CLUB_S1996_97_0022</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43234,12 +43482,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0014</t>
+          <t>CLUB_S1996_97_0026</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43254,12 +43502,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0022</t>
+          <t>CLUB_S1996_97_0041</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43274,12 +43522,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0026</t>
+          <t>CLUB_S1996_97_0062</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43294,12 +43542,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0041</t>
+          <t>CLUB_S1996_97_0066</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43314,12 +43562,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0042</t>
+          <t>CLUB_S1996_97_0083</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43334,12 +43582,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0062</t>
+          <t>CLUB_S1996_97_0107</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43354,12 +43602,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0066</t>
+          <t>CLUB_S1996_97_0156</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43374,12 +43622,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0067</t>
+          <t>CLUB_S1996_97_0165</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43394,12 +43642,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0083</t>
+          <t>CLUB_S1996_97_0175</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43414,12 +43662,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0107</t>
+          <t>CLUB_S1996_97_0181</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43434,12 +43682,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0152</t>
+          <t>CLUB_S1996_97_0182</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43454,12 +43702,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0156</t>
+          <t>CLUB_S1996_97_0184</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43474,12 +43722,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0156</t>
+          <t>CLUB_S1996_97_0192</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43494,12 +43742,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0165</t>
+          <t>CLUB_S1996_97_0210</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43514,12 +43762,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0165</t>
+          <t>CLUB_S1996_97_0250</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -43534,12 +43782,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0166</t>
+          <t>CLUB_S1996_97_0251</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43554,12 +43802,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0175</t>
+          <t>CLUB_S1996_97_0256</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43574,12 +43822,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0181</t>
+          <t>CLUB_S1996_97_0260</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -43594,12 +43842,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0182</t>
+          <t>CLUB_S1996_97_0262</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43614,12 +43862,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0184</t>
+          <t>CLUB_S1996_97_0266</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43634,12 +43882,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0192</t>
+          <t>CLUB_S1996_97_0288</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -43654,12 +43902,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0210</t>
+          <t>CLUB_S1996_97_0294</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43674,12 +43922,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0250</t>
+          <t>CLUB_S1996_97_0304</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -43694,12 +43942,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0251</t>
+          <t>CLUB_S1996_97_0384</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
     </row>
@@ -43714,12 +43962,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0256</t>
+          <t>CLUB_S1996_97_0401</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43734,12 +43982,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0260</t>
+          <t>CLUB_S1996_97_0401</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43754,12 +44002,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0262</t>
+          <t>CLUB_S1996_97_0408</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43774,12 +44022,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0266</t>
+          <t>CLUB_S1996_97_0409</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43794,12 +44042,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0288</t>
+          <t>CLUB_S1996_97_0435</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43814,12 +44062,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0294</t>
+          <t>CLUB_S1996_97_0441</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43834,12 +44082,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0304</t>
+          <t>CLUB_S1996_97_0468</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43854,177 +44102,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0401</t>
+          <t>CLUB_S1996_97_0471</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0401</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0408</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0409</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0435</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0441</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0447</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0468</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1996_97_0471</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -27,7 +27,7 @@
     <sheet name="TODO" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -16396,7 +16396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16444,21 +16444,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] Cheb — odstoupil (club_id: CLUB_S1996_97_0248)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -16470,7 +16475,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -16482,7 +16487,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -16494,7 +16499,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -16506,7 +16511,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -16518,7 +16523,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -16530,7 +16535,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16542,7 +16547,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16566,7 +16571,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16578,7 +16583,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16614,7 +16619,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -16626,7 +16631,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -16638,7 +16643,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16650,7 +16655,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'Cheb — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16662,7 +16667,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16674,7 +16679,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -16686,7 +16691,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16698,7 +16703,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16710,7 +16715,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -16722,7 +16727,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -16734,7 +16739,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16746,7 +16751,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16758,7 +16763,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -16770,7 +16775,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16782,7 +16787,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16794,7 +16799,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16806,7 +16811,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16818,7 +16823,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16830,7 +16835,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16842,10 +16847,34 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -33586,7 +33615,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Lokomotiva Cheb. city OK. || Lokomotiva Cheb 58/59 - PRVNI vyskyt Lokomotivy (zeleznicarsky klub - 1960 oficialni nazev TJ Lokomotiva Cheb). Cheb = HC Stadion Cheb (Wiki D42 + hokej.cz 04/2026). Genealogie: Cheb (49/50 prirodni led v Gottwaldovych sadech) -&gt; RH Cheb (51/52+ bezpecnostni klub Rude hvezdy) + Lokomotiva Cheb (zeleznicarsky klub TJ Lokomotiva Cheb od 1960) + Spartak Cheb (paralelni podnikovy) + DA Hvezda + Slavoj. **DNESNI HC Stadion Cheb zalozen 1978** jako TJ Stadion Cheb (Wiki) -&gt; 2008 HC Stadion Cheb. Patterns: Cheb, RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvězda Cheb. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). KLICOVY ROK 1958 prejmenovani Železničáři -&gt; Lokomotiva. Lokomotiva Cheb = TJ Lokomotiva Cheb (Wiki D42 - registr ustavy 04/2026). Klub zaleznicaru. Genealogie: Železničáři Cheb (1951+) -&gt; Lokomotiva Cheb (1958+, DSO reforma + zmena na Lokomotiva). 'Dnesni nazev TJ Lokomotiva Cheb je od roku 1960' (podle TJ Lokomotiva oficial). Hokejovy oddil: 50.leta hriste v Gottwaldovych sadech na prirodnim lede. Paralelni od RH/Spartak/Stadion chebskych klubu. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). PRVNI vyskyt Lokomotivy Cheb (oficialni TJ od 1960). Předchudce Železničáři Cheb. Cheb (Wiki D42 + retromuseum.cz - registr ustavy 04/2026). MULTI-CHAIN MESTO - v 50.letech 4-5 paralelnich klubu. **HC Stadion Cheb** (1978-dnes, ZALOZEN 1978 jako TJ Stadion Cheb, 2008 prejmenovan): to je dnesni klub HOKEJE - vznikl ZNOVA, NENI primy nasledník zadneho 50.letech. **RH Cheb** (1951-1996): klub 5. brigady Pohranicni straze (DSO Ministerstva vnitra). Vojenska sokolska jednota Sokolovo (1951) -&gt; RH (1952+) -&gt; VTJ Dukla Hranicar (1966-1972, pod MO) -&gt; RH zpet -&gt; 1990 SK policie Union -&gt; FC Union -&gt; 1996 zanik. **TJ Lokomotiva Cheb** (oficialne 1960): zeleznicarsky klub, oddil hokeje od 50. let (1957 hraje na priroduicm lede v Gottwaldovych sadech). Sportovni areal Lokomotiva v Hradcanech (mestska cast Chebu). **Spartak Cheb / Eska**: stadion Esky Cheb, v 1952 prejmenovany Spartak Eska Cheb, v 1963 Spartak se stal soucasti RH Cheb. **DA Hvezda Cheb**: drobny **Slavoj Cheb**: drobny Patterns: RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvezda Cheb, Slavoj Cheb. city Cheb. POZOR: Tatran Luby u Chebu = JINE MESTO (Luby jsou samostatne mesto).</t>
+          <t>Lokomotiva Cheb. city OK. || Lokomotiva Cheb 58/59 - PRVNI vyskyt Lokomotivy (zeleznicarsky klub - 1960 oficialni nazev TJ Lokomotiva Cheb). Cheb = HC Stadion Cheb (Wiki D42 + hokej.cz 04/2026). Genealogie: Cheb (49/50 prirodni led v Gottwaldovych sadech) -&gt; RH Cheb (51/52+ bezpecnostni klub Rude hvezdy) + Lokomotiva Cheb (zeleznicarsky klub TJ Lokomotiva Cheb od 1960) + Spartak Cheb (paralelni podnikovy) + DA Hvezda + Slavoj. **DNESNI HC Stadion Cheb zalozen 1978** jako TJ Stadion Cheb (Wiki) -&gt; 2008 HC Stadion Cheb. Patterns: Cheb, RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvězda Cheb. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). KLICOVY ROK 1958 prejmenovani Železničáři -&gt; Lokomotiva. Lokomotiva Cheb = TJ Lokomotiva Cheb (Wiki D42 - registr ustavy 04/2026). Klub zaleznicaru. Genealogie: Železničáři Cheb (1951+) -&gt; Lokomotiva Cheb (1958+, DSO reforma + zmena na Lokomotiva). 'Dnesni nazev TJ Lokomotiva Cheb je od roku 1960' (podle TJ Lokomotiva oficial). Hokejovy oddil: 50.leta hriste v Gottwaldovych sadech na prirodnim lede. Paralelni od RH/Spartak/Stadion chebskych klubu. city Cheb. || Lokomotiva Cheb 58/59 (40_Karlovarský). PRVNI vyskyt Lokomotivy Cheb (oficialni TJ od 1960). Předchudce Železničáři Cheb. Cheb (Wiki D42 + retromuseum.cz - registr ustavy 04/2026). MULTI-CHAIN MESTO - v 50.letech 4-5 paralelnich klubu. **HC Stadion Cheb** (1978-dnes, ZALOZEN 1978 jako TJ Stadion Cheb, 2008 prejmenovan): to je dnesni klub HOKEJE - vznikl ZNOVA, NENI primy nasledník zadneho 50.letech. **RH Cheb** (1951-1996): klub 5. brigady Pohranicni straze (DSO Ministerstva vnitra). Vojenska sokolska jednota Sokolovo (1951) -&gt; RH (1952+) -&gt; VTJ Dukla Hranicar (1966-1972, pod MO) -&gt; RH zpet -&gt; 1990 SK policie Union -&gt; FC Union -&gt; 1996 zanik. **TJ Lokomotiva Cheb** (oficialne 1960): zeleznicarsky klub, oddil hokeje od 50. let (1957 hraje na priroduicm lede v Gottwaldovych sadech). Sportovni areal Lokomotiva v Hradcanech (mestska cast Chebu). **Spartak Cheb / Eska**: stadion Esky Cheb, v 1952 prejmenovany Spartak Eska Cheb, v 1963 Spartak se stal soucasti RH Cheb. **DA Hvezda Cheb**: drobny **Slavoj Cheb**: drobny Patterns: RH Cheb, Spartak Cheb, Lokomotiva Cheb, DA Hvezda Cheb, Slavoj Cheb. city Cheb. POZOR: Tatran Luby u Chebu = JINE MESTO (Luby jsou samostatne mesto). || TBD: extrahováno z block_name: 'Cheb — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -43388,7 +43417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -43762,12 +43791,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0250</t>
+          <t>CLUB_S1996_97_0248</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: extrahováno z block_name: 'Cheb — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -43782,12 +43811,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0251</t>
+          <t>CLUB_S1996_97_0250</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -43802,12 +43831,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0256</t>
+          <t>CLUB_S1996_97_0251</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43822,12 +43851,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0260</t>
+          <t>CLUB_S1996_97_0256</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43842,12 +43871,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0262</t>
+          <t>CLUB_S1996_97_0260</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -43862,12 +43891,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0266</t>
+          <t>CLUB_S1996_97_0262</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -43882,12 +43911,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0288</t>
+          <t>CLUB_S1996_97_0266</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43902,12 +43931,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0294</t>
+          <t>CLUB_S1996_97_0288</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -43922,12 +43951,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0304</t>
+          <t>CLUB_S1996_97_0294</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -43942,12 +43971,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0384</t>
+          <t>CLUB_S1996_97_0304</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -43962,12 +43991,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0401</t>
+          <t>CLUB_S1996_97_0384</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
       </c>
     </row>
@@ -43987,7 +44016,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -44002,12 +44031,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0408</t>
+          <t>CLUB_S1996_97_0401</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44022,7 +44051,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0409</t>
+          <t>CLUB_S1996_97_0408</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -44042,12 +44071,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0435</t>
+          <t>CLUB_S1996_97_0409</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44062,12 +44091,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0441</t>
+          <t>CLUB_S1996_97_0435</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -44082,12 +44111,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1996_97_0468</t>
+          <t>CLUB_S1996_97_0441</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -44102,17 +44131,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>CLUB_S1996_97_0468</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>CLUB_S1996_97_0471</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -62183,7 +62232,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Krajská soutěž / skupina B / Cheb — odstoupil</t>
+          <t>Krajská soutěž / skupina B</t>
         </is>
       </c>
       <c r="C22" s="2" t="n"/>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -44897,7 +44897,7 @@
         <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -45064,7 +45064,7 @@
         <v>155</v>
       </c>
       <c r="M12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M13" t="n">
         <v>49</v>
@@ -46251,7 +46251,7 @@
         <v>9</v>
       </c>
       <c r="J9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -46337,7 +46337,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M10" t="n">
         <v>32</v>
@@ -46966,7 +46966,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M18" t="n">
         <v>16</v>
@@ -47036,7 +47036,7 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -16891,7 +16891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16955,6 +16955,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20673,8 +20683,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -20804,7 +20812,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -17143,6 +17143,16 @@
           <t>NODE_S1996_97_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17157,6 +17167,14 @@
         <is>
           <t>NODE_S1995_96_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -17331,6 +17349,16 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17345,6 +17373,14 @@
         <is>
           <t>NODE_S1995_96_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -17425,6 +17461,16 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17439,6 +17485,14 @@
         <is>
           <t>NODE_S1995_96_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -17472,6 +17526,16 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17486,6 +17550,14 @@
         <is>
           <t>NODE_S1995_96_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -17519,6 +17591,8 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17533,6 +17607,14 @@
         <is>
           <t>NODE_S1995_96_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -17566,6 +17648,8 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17580,6 +17664,14 @@
         <is>
           <t>NODE_S1995_96_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -17613,6 +17705,8 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17627,6 +17721,14 @@
         <is>
           <t>NODE_S1995_96_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -17660,6 +17762,8 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17674,6 +17778,14 @@
         <is>
           <t>NODE_S1995_96_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -17707,6 +17819,8 @@
           <t>NODE_S1996_97_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17721,6 +17835,14 @@
         <is>
           <t>NODE_S1995_96_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -17754,6 +17876,8 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17768,6 +17892,14 @@
         <is>
           <t>NODE_S1995_96_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -17801,6 +17933,8 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17815,6 +17949,14 @@
         <is>
           <t>NODE_S1995_96_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -17848,6 +17990,16 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17862,6 +18014,14 @@
         <is>
           <t>NODE_S1995_96_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -17989,6 +18149,12 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18003,6 +18169,14 @@
         <is>
           <t>NODE_S1995_96_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -18036,6 +18210,12 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18050,6 +18230,14 @@
         <is>
           <t>NODE_S1995_96_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -18083,6 +18271,12 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18097,6 +18291,14 @@
         <is>
           <t>NODE_S1995_96_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -18130,6 +18332,12 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18144,6 +18352,14 @@
         <is>
           <t>NODE_S1995_96_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -18177,6 +18393,8 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18191,6 +18409,14 @@
         <is>
           <t>NODE_S1995_96_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -18815,6 +19041,16 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0043</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0044</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18824,6 +19060,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -18857,6 +19101,8 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18871,6 +19117,14 @@
         <is>
           <t>NODE_S1995_96_0048</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -18904,6 +19158,8 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18918,6 +19174,14 @@
         <is>
           <t>NODE_S1995_96_0050</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>-1.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -19119,6 +19383,8 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19128,6 +19394,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -19161,6 +19435,8 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19170,6 +19446,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>-1.–7. ZČ</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -19297,6 +19581,12 @@
           <t>NODE_S1996_97_0051</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0054</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19311,6 +19601,14 @@
         <is>
           <t>NODE_S1995_96_0053</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -19344,6 +19642,8 @@
           <t>NODE_S1996_97_0051</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19358,6 +19658,14 @@
         <is>
           <t>NODE_S1995_96_0054</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -20143,6 +20451,8 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20157,6 +20467,14 @@
         <is>
           <t>NODE_S1995_96_0072</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -20410,6 +20728,8 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20419,6 +20739,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -20452,6 +20780,8 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20461,6 +20791,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -20536,6 +20874,8 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20545,6 +20885,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -20578,6 +20926,8 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20587,6 +20937,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -20683,6 +21041,8 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -20812,6 +21172,7 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -753,6 +753,11 @@
           <t>HC Petra Vsetín</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>52</v>
       </c>
@@ -17591,8 +17596,6 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17648,8 +17651,6 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17705,8 +17706,6 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17762,8 +17761,6 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17819,8 +17816,6 @@
           <t>NODE_S1996_97_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17876,8 +17871,6 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17933,8 +17926,6 @@
           <t>NODE_S1996_97_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18154,7 +18145,6 @@
           <t>NODE_S1996_97_0023</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18215,7 +18205,6 @@
           <t>NODE_S1996_97_0024</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18276,7 +18265,6 @@
           <t>NODE_S1996_97_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18337,7 +18325,6 @@
           <t>NODE_S1996_97_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18393,8 +18380,6 @@
           <t>NODE_S1996_97_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19101,8 +19086,6 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19158,8 +19141,6 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19383,8 +19364,6 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19435,8 +19414,6 @@
           <t>NODE_S1996_97_0040</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19586,7 +19563,6 @@
           <t>NODE_S1996_97_0054</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19642,8 +19618,6 @@
           <t>NODE_S1996_97_0051</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20451,8 +20425,6 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20728,8 +20700,6 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20780,8 +20750,6 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20874,8 +20842,6 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20926,8 +20892,6 @@
           <t>NODE_S1996_97_0067</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21041,8 +21005,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -21172,7 +21134,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -43527,7 +43488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43771,6 +43732,18 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>Zdrojový konflikt ponechán otevřený: Liberec PTS 51 (XLS/XLSX) vs 50 (PDF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HC Petra Vsetín</t>
         </is>
       </c>
     </row>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -21005,6 +21005,8 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -21134,6 +21136,7 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -36,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -108,6 +117,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26201,8 +26212,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -26332,7 +26341,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -56650,7 +56658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56707,7 +56715,7 @@
           <t>CLUB_S1996_97_0004</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56727,7 +56735,7 @@
           <t>CLUB_S1996_97_0022</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56747,7 +56755,7 @@
           <t>CLUB_S1996_97_0026</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56767,7 +56775,7 @@
           <t>CLUB_S1996_97_0041</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56787,7 +56795,7 @@
           <t>CLUB_S1996_97_0062</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56807,7 +56815,7 @@
           <t>CLUB_S1996_97_0066</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56827,7 +56835,7 @@
           <t>CLUB_S1996_97_0083</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0091 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -56847,7 +56855,7 @@
           <t>CLUB_S1996_97_0107</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0104 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -56867,7 +56875,7 @@
           <t>CLUB_S1996_97_0156</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56887,7 +56895,7 @@
           <t>CLUB_S1996_97_0165</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56907,7 +56915,7 @@
           <t>CLUB_S1996_97_0175</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56927,7 +56935,7 @@
           <t>CLUB_S1996_97_0181</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56947,7 +56955,7 @@
           <t>CLUB_S1996_97_0182</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56967,7 +56975,7 @@
           <t>CLUB_S1996_97_0184</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -56987,7 +56995,7 @@
           <t>CLUB_S1996_97_0192</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0192 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57007,7 +57015,7 @@
           <t>CLUB_S1996_97_0210</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Klub rozhodčích LH Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57027,7 +57035,7 @@
           <t>CLUB_S1996_97_0248</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'Cheb — odstoupil' [fix_club_notes_in_block_name]</t>
         </is>
@@ -57047,7 +57055,7 @@
           <t>CLUB_S1996_97_0250</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -57067,7 +57075,7 @@
           <t>CLUB_S1996_97_0251</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -57087,7 +57095,7 @@
           <t>CLUB_S1996_97_0256</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -57107,7 +57115,7 @@
           <t>CLUB_S1996_97_0260</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -57127,7 +57135,7 @@
           <t>CLUB_S1996_97_0262</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57147,7 +57155,7 @@
           <t>CLUB_S1996_97_0266</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0285 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57167,7 +57175,7 @@
           <t>CLUB_S1996_97_0288</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -57187,7 +57195,7 @@
           <t>CLUB_S1996_97_0294</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0274 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57207,7 +57215,7 @@
           <t>CLUB_S1996_97_0304</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -57227,7 +57235,7 @@
           <t>CLUB_S1996_97_0384</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: D44 můstek prev_club_id → CLUB_S1995_96_0380 (stejné city+jádro, org. reforma) [fix_d44_bridges]</t>
         </is>
@@ -57247,7 +57255,7 @@
           <t>CLUB_S1996_97_0401</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0399 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57267,7 +57275,7 @@
           <t>CLUB_S1996_97_0401</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: city 'Z club Zlín' → 'Zlín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57287,7 +57295,7 @@
           <t>CLUB_S1996_97_0408</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57307,7 +57315,7 @@
           <t>CLUB_S1996_97_0409</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57327,7 +57335,7 @@
           <t>CLUB_S1996_97_0435</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'NH Válcovny Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -57347,7 +57355,7 @@
           <t>CLUB_S1996_97_0441</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0414 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57367,7 +57375,7 @@
           <t>CLUB_S1996_97_0468</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0160 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -57387,11 +57395,37 @@
           <t>CLUB_S1996_97_0471</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1995_96_0344 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Středočeský – Regionální přebor I.třídy (Středočeský kraj) · NODE_S1996_97_0084</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (Kladno 1988, HC Dobříš), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F36"/>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +119,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21608,7 +21611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22087,6 +22090,23 @@
         </is>
       </c>
       <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NODE_S1996_97_0084</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (Kladno 1988, HC Dobříš), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -57415,7 +57435,7 @@
           <t>Středočeský – Regionální přebor I.třídy (Středočeský kraj) · NODE_S1996_97_0084</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (Kladno 1988, HC Dobříš), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -23743,7 +23743,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -23832,7 +23832,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -24141,7 +24141,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální přebor I.třídy</t>
+          <t>Středočeský, 4. úroveň Regionální přebor I.třídy</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -24290,7 +24290,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finále</t>
+          <t>Středočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 o udržení</t>
+          <t>Středočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Regionální přebor II.třídy</t>
+          <t>Středočeský, 4. úroveň Regionální přebor II.třídy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A</t>
+          <t>Středočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B</t>
+          <t>Středočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finálová skupina</t>
+          <t>Středočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -24568,7 +24568,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finále</t>
+          <t>Středočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -24618,7 +24618,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 o udržení</t>
+          <t>Středočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -24715,7 +24715,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -24762,7 +24762,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 finále</t>
+          <t>Jihočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -24877,7 +24877,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Krajská soutěž</t>
+          <t>Jihočeský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 Krajská soutěž</t>
+          <t>Západočeský, 4. úroveň Krajská soutěž</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -25065,7 +25065,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina A</t>
+          <t>Západočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -25112,7 +25112,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina B</t>
+          <t>Západočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -25159,7 +25159,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -25206,7 +25206,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -25300,7 +25300,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -25347,7 +25347,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina sever</t>
+          <t>Východočeský, 5. úroveň, skupina sever</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -25394,7 +25394,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L50 skupina jih</t>
+          <t>Východočeský, 5. úroveň, skupina jih</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -25535,7 +25535,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -25629,7 +25629,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -25684,7 +25684,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -25731,7 +25731,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -25778,7 +25778,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina C</t>
+          <t>Jihomoravský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -25820,7 +25820,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina D</t>
+          <t>Jihomoravský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -25862,7 +25862,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina A+B</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina A+B</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -25904,7 +25904,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení A</t>
+          <t>Jihomoravský, 4. úroveň o udržení A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -25954,7 +25954,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení B</t>
+          <t>Jihomoravský, 4. úroveň o udržení B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -26004,7 +26004,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finálová skupina C+D</t>
+          <t>Jihomoravský, 4. úroveň finálová skupina C+D</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení A</t>
+          <t>Jihomoravský, 4. úroveň o udržení A</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 o udržení B</t>
+          <t>Jihomoravský, 4. úroveň o udržení B</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -26146,7 +26146,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -26193,7 +26193,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -26232,6 +26232,8 @@
         </is>
       </c>
     </row>
+    <row r="83"/>
+    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -26264,7 +26266,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -26361,6 +26363,7 @@
         </is>
       </c>
     </row>
+    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>

--- a/data/S1996_97_FINAL.xlsx
+++ b/data/S1996_97_FINAL.xlsx
@@ -26232,8 +26232,6 @@
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84"/>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
@@ -26363,7 +26361,6 @@
         </is>
       </c>
     </row>
-    <row r="92"/>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
@@ -64471,7 +64468,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -64627,7 +64624,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -66897,7 +66894,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
